--- a/data/raw/aisvn/IFTTT_aisvn (24).xlsx
+++ b/data/raw/aisvn/IFTTT_aisvn (24).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Agents\opencode\solardata\data\raw\aisvn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5398AD78-66C0-4EA9-8AF2-A35932D1D05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F49299-A81F-4678-A458-48CE92D011AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="465" windowWidth="23655" windowHeight="15255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7785" yWindow="1185" windowWidth="19260" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6068,7 +6068,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6079,6 +6079,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEA9999"/>
         <bgColor rgb="FFEA9999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -6094,7 +6106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6102,6 +6114,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19744,58 +19758,72 @@
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A384" s="3" t="s">
+      <c r="A384" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="B384" s="3">
-        <v>123</v>
-      </c>
-      <c r="C384" s="3">
-        <v>456</v>
-      </c>
-      <c r="D384" s="3">
-        <v>789</v>
-      </c>
-      <c r="E384" s="3"/>
-      <c r="F384" s="3"/>
-      <c r="G384" s="3"/>
-      <c r="H384" s="3"/>
-      <c r="I384" s="3"/>
-      <c r="J384" s="3"/>
-      <c r="K384" s="3"/>
+      <c r="B384" s="5">
+        <v>18.7</v>
+      </c>
+      <c r="C384" s="5">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D384" s="5">
+        <v>-1.8</v>
+      </c>
+      <c r="E384" s="5">
+        <v>-33.1</v>
+      </c>
+      <c r="F384" s="5">
+        <v>17.8</v>
+      </c>
+      <c r="G384" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="H384" s="5">
+        <v>34.5</v>
+      </c>
+      <c r="I384" s="5">
+        <v>3.62</v>
+      </c>
+      <c r="J384" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="K384" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A385" s="3" t="s">
+      <c r="A385" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="B385" s="3">
+      <c r="B385" s="6">
         <v>19.12</v>
       </c>
-      <c r="C385" s="3">
+      <c r="C385" s="6">
         <v>18.510000000000002</v>
       </c>
-      <c r="D385" s="3">
+      <c r="D385" s="6">
         <v>-1.76</v>
       </c>
-      <c r="E385" s="3">
+      <c r="E385" s="6">
         <v>-33.75</v>
       </c>
-      <c r="F385" s="3">
+      <c r="F385" s="6">
         <v>17.899999999999999</v>
       </c>
-      <c r="G385" s="3">
+      <c r="G385" s="6">
         <v>0.4</v>
       </c>
-      <c r="H385" s="3">
+      <c r="H385" s="6">
         <v>59.9</v>
       </c>
-      <c r="I385" s="3">
+      <c r="I385" s="6">
         <v>3.62</v>
       </c>
-      <c r="J385" s="3">
+      <c r="J385" s="6">
         <v>2.7</v>
       </c>
-      <c r="K385" s="3">
+      <c r="K385" s="6">
         <v>1</v>
       </c>
     </row>
